--- a/artfynd/A 19265-2025 artfynd.xlsx
+++ b/artfynd/A 19265-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125194949</v>
+        <v>125194953</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592566</v>
+        <v>592520</v>
       </c>
       <c r="R2" t="n">
-        <v>6984946</v>
+        <v>6984906</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125194953</v>
+        <v>125194949</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592520</v>
+        <v>592566</v>
       </c>
       <c r="R3" t="n">
-        <v>6984906</v>
+        <v>6984946</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -863,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 19265-2025 artfynd.xlsx
+++ b/artfynd/A 19265-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125194953</v>
+        <v>125194949</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592520</v>
+        <v>592566</v>
       </c>
       <c r="R2" t="n">
-        <v>6984906</v>
+        <v>6984946</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125194949</v>
+        <v>125194953</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592566</v>
+        <v>592520</v>
       </c>
       <c r="R3" t="n">
-        <v>6984946</v>
+        <v>6984906</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -858,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 19265-2025 artfynd.xlsx
+++ b/artfynd/A 19265-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125194949</v>
+        <v>125194953</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592566</v>
+        <v>592520</v>
       </c>
       <c r="R2" t="n">
-        <v>6984946</v>
+        <v>6984906</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125194953</v>
+        <v>125194949</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592520</v>
+        <v>592566</v>
       </c>
       <c r="R3" t="n">
-        <v>6984906</v>
+        <v>6984946</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -863,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 19265-2025 artfynd.xlsx
+++ b/artfynd/A 19265-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>125194953</v>
       </c>
       <c r="B2" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,12 +775,7 @@
         <v>125194949</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19265-2025 artfynd.xlsx
+++ b/artfynd/A 19265-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125194949</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19265-2025 artfynd.xlsx
+++ b/artfynd/A 19265-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125194949</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19265-2025 artfynd.xlsx
+++ b/artfynd/A 19265-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125194949</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
